--- a/warehouse_gui_server/사용자2주문.xlsx
+++ b/warehouse_gui_server/사용자2주문.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
